--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(1).xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="408">
   <si>
     <t>ID</t>
   </si>
@@ -96,10 +96,18 @@
     <t>通往四层的楼道很长，逼仄的走廊将你们的影子压成窄窄的一条，拖在积灰的地板上，像两只在狭长试管中穿行的蝌蚪。</t>
   </si>
   <si>
+    <t>14 enhanced_horror-free</t>
+  </si>
+  <si>
     <t>loadScript(sntzm_clark3F(2), 2)</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>源类型</t>
     </r>
     <r>
@@ -201,10 +209,18 @@
     <t>他们把人变成了活着的兵器。</t>
   </si>
   <si>
+    <t>7 enhanced litesaturation-horror</t>
+  </si>
+  <si>
     <t>bgfade(sntzm_ss_76,1)</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>源类型</t>
     </r>
     <r>
@@ -2787,24 +2803,24 @@
         <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="150" spans="1:12">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
@@ -2819,24 +2835,24 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" ht="27" spans="1:12">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2854,7 +2870,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -2866,24 +2882,24 @@
         <v>15</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" ht="28.5" spans="1:12">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
         <v>15</v>
@@ -2892,7 +2908,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -2904,15 +2920,15 @@
         <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" ht="43.5" spans="1:12">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2921,7 +2937,7 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
@@ -2930,7 +2946,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -2942,24 +2958,24 @@
         <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
@@ -2968,7 +2984,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -2980,15 +2996,15 @@
         <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" ht="54" spans="1:12">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -2997,7 +3013,7 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
         <v>15</v>
@@ -3006,7 +3022,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -3018,15 +3034,15 @@
         <v>15</v>
       </c>
       <c r="K9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" ht="27" spans="1:12">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -3044,7 +3060,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -3059,21 +3075,21 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
@@ -3082,7 +3098,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3094,15 +3110,15 @@
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" ht="40.5" spans="1:12">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -3111,7 +3127,7 @@
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -3120,7 +3136,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3135,21 +3151,21 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" ht="42" spans="1:12">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3158,7 +3174,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3173,21 +3189,21 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="42" spans="1:12">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3196,7 +3212,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3211,12 +3227,12 @@
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" ht="27" spans="1:12">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3225,7 +3241,7 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E15" t="s">
         <v>15</v>
@@ -3234,7 +3250,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3249,21 +3265,21 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" ht="42" spans="1:12">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3272,7 +3288,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3284,12 +3300,12 @@
         <v>15</v>
       </c>
       <c r="L16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" ht="40.5" spans="1:12">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3298,7 +3314,7 @@
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3307,7 +3323,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3319,24 +3335,24 @@
         <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" ht="27" spans="1:12">
       <c r="A18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3345,7 +3361,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3357,33 +3373,33 @@
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -3395,15 +3411,15 @@
         <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L19" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" ht="28.5" spans="1:12">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3412,16 +3428,16 @@
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s">
         <v>15</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3433,24 +3449,24 @@
         <v>15</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="L20" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" ht="55.5" spans="1:12">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3459,7 +3475,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3471,24 +3487,24 @@
         <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" ht="27" spans="1:12">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3497,7 +3513,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3509,15 +3525,15 @@
         <v>15</v>
       </c>
       <c r="K22" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L22" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" ht="40.5" spans="1:12">
       <c r="A23" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3535,7 +3551,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3550,15 +3566,15 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" ht="27" spans="1:12">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
@@ -3573,7 +3589,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3588,12 +3604,12 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" ht="54" spans="1:12">
       <c r="A25" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3611,7 +3627,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3626,15 +3642,15 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" ht="27" spans="1:12">
       <c r="A26" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
@@ -3649,7 +3665,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3664,21 +3680,21 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" ht="27" spans="1:12">
       <c r="A27" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3687,7 +3703,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3699,24 +3715,24 @@
         <v>15</v>
       </c>
       <c r="K27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L27" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" ht="40.5" spans="1:12">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3725,7 +3741,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3737,24 +3753,24 @@
         <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -3763,7 +3779,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3775,15 +3791,15 @@
         <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L29" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" ht="40.5" spans="1:12">
       <c r="A30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3792,7 +3808,7 @@
         <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -3801,7 +3817,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3813,18 +3829,18 @@
         <v>15</v>
       </c>
       <c r="K30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" ht="27" spans="1:12">
       <c r="A31" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
         <v>14</v>
@@ -3839,7 +3855,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3854,12 +3870,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" ht="27" spans="1:12">
       <c r="A32" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3877,7 +3893,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3892,15 +3908,15 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" ht="40.5" spans="1:12">
       <c r="A33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
@@ -3915,7 +3931,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3930,12 +3946,12 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" ht="27" spans="1:12">
       <c r="A34" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -3953,7 +3969,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3968,15 +3984,15 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
@@ -3991,7 +4007,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -4006,12 +4022,12 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36" ht="40.5" spans="1:12">
       <c r="A36" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -4029,7 +4045,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4044,21 +4060,21 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" ht="28.5" spans="1:12">
       <c r="A37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4067,7 +4083,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4079,24 +4095,24 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L37" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" ht="28.5" spans="1:12">
       <c r="A38" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
         <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4105,7 +4121,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4120,12 +4136,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" ht="27" spans="1:12">
       <c r="A39" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4134,7 +4150,7 @@
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4143,7 +4159,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4158,21 +4174,21 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C40" t="s">
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4181,7 +4197,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4196,12 +4212,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41" ht="54" spans="1:12">
       <c r="A41" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4210,7 +4226,7 @@
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4219,7 +4235,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4231,15 +4247,15 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L41" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" ht="54" spans="1:12">
       <c r="A42" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4257,7 +4273,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4272,15 +4288,15 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" ht="55.5" spans="1:12">
       <c r="A43" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B43" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C43" t="s">
         <v>14</v>
@@ -4295,7 +4311,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4310,12 +4326,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" ht="40.5" spans="1:12">
       <c r="A44" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4333,7 +4349,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4348,21 +4364,21 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" ht="28.5" spans="1:12">
       <c r="A45" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B45" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4371,7 +4387,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4383,15 +4399,15 @@
         <v>15</v>
       </c>
       <c r="K45" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L45" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4400,7 +4416,7 @@
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -4421,15 +4437,15 @@
         <v>15</v>
       </c>
       <c r="K46" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L46" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" ht="90" spans="1:12">
       <c r="A47" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4447,7 +4463,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4459,15 +4475,15 @@
         <v>15</v>
       </c>
       <c r="K47" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L47" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" ht="90" spans="1:12">
       <c r="A48" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4485,7 +4501,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4500,21 +4516,21 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" ht="40.5" spans="1:12">
       <c r="A49" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B49" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -4523,7 +4539,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4535,24 +4551,24 @@
         <v>15</v>
       </c>
       <c r="K49" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L49" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" ht="42" spans="1:12">
       <c r="A50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B50" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E50" t="s">
         <v>15</v>
@@ -4561,7 +4577,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4573,15 +4589,15 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L50" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" ht="27" spans="1:12">
       <c r="A51" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4599,7 +4615,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4614,15 +4630,15 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52" ht="54" spans="1:12">
       <c r="A52" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B52" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
@@ -4637,7 +4653,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4652,15 +4668,15 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" ht="28.5" spans="1:12">
       <c r="A53" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B53" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
@@ -4675,7 +4691,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4690,12 +4706,12 @@
         <v>15</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="54" ht="40.5" spans="1:12">
       <c r="A54" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4713,7 +4729,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4728,12 +4744,12 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" ht="40.5" spans="1:12">
       <c r="A55" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4751,7 +4767,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4766,12 +4782,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" ht="28.5" spans="1:12">
       <c r="A56" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4789,7 +4805,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4804,21 +4820,21 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -4827,7 +4843,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4839,15 +4855,15 @@
         <v>15</v>
       </c>
       <c r="K57" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L57" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="58" ht="54" spans="1:12">
       <c r="A58" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4856,7 +4872,7 @@
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -4865,7 +4881,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4877,15 +4893,15 @@
         <v>15</v>
       </c>
       <c r="K58" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="L58" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="59" ht="40.5" spans="1:12">
       <c r="A59" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4903,7 +4919,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4918,12 +4934,12 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="60" ht="54" spans="1:12">
       <c r="A60" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4941,7 +4957,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4956,12 +4972,12 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61" ht="40.5" spans="1:12">
       <c r="A61" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -4979,7 +4995,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -4991,18 +5007,18 @@
         <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="L61" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>209</v>
-      </c>
-      <c r="B62" t="s">
-        <v>13</v>
+        <v>211</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="C62" t="s">
         <v>14</v>
@@ -5017,7 +5033,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5032,15 +5048,15 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="63" ht="27" spans="1:12">
       <c r="A63" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B63" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
@@ -5055,7 +5071,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5070,12 +5086,12 @@
         <v>15</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="64" ht="54" spans="1:12">
       <c r="A64" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5093,7 +5109,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5105,15 +5121,15 @@
         <v>15</v>
       </c>
       <c r="K64" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L64" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="65" ht="27" spans="1:12">
       <c r="A65" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5131,7 +5147,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5146,15 +5162,15 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="66" ht="27" spans="1:12">
       <c r="A66" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B66" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
@@ -5169,7 +5185,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5184,12 +5200,12 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="67" ht="40.5" spans="1:12">
       <c r="A67" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5207,7 +5223,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5219,10 +5235,10 @@
         <v>15</v>
       </c>
       <c r="K67" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L67" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -5243,47 +5259,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
@@ -5291,7 +5307,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -5299,66 +5315,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B10" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B11" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B14" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B15" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -5380,616 +5396,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B7" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E7" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B8" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D8" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D9" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E10" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B11" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C11" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D11" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E11" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F11" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B12" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C12" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D12" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E12" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F12" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B13" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C13" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D13" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E13" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B14" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D14" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E14" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F14" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B15" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C15" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D15" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F15" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B16" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C16" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D16" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E16" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F16" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B17" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C17" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D17" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E17" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F17" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B18" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C18" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D18" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E18" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F18" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B19" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C19" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D19" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E19" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F19" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B20" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C20" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D20" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E20" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F20" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B21" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C21" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D21" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E21" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F21" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B22" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C22" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D22" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E22" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F22" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B23" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C23" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D23" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E23" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F23" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B24" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C24" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D24" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E24" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F24" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B25" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C25" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D25" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E25" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F25" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B26" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C26" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D26" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E26" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F26" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B27" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C27" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D27" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E27" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F27" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B28" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C28" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D28" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E28" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F28" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B29" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C29" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D29" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E29" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F29" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B30" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C30" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D30" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E30" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F30" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B31" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C31" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D31" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(1).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_克拉克线3层（上）" sheetId="1" r:id="rId1"/>
@@ -99,7 +99,7 @@
     <t>14 enhanced_horror-free</t>
   </si>
   <si>
-    <t>loadScript(sntzm_clark3F(2), 2)</t>
+    <t>bgfade(sntzm_clark3F(1)_67,1)&amp;loadScript(sntzm_clark3F(2), 2)&amp;unlockmusic(Music14)</t>
   </si>
   <si>
     <r>
@@ -212,7 +212,7 @@
     <t>7 enhanced litesaturation-horror</t>
   </si>
   <si>
-    <t>bgfade(sntzm_ss_76,1)</t>
+    <t>bgfade(sntzm_ss_76,1)&amp;unlockmusic(Music7)</t>
   </si>
   <si>
     <r>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(1).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20385" windowHeight="10605"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_克拉克线3层（上）" sheetId="1" r:id="rId1"/>
@@ -99,7 +99,7 @@
     <t>14 enhanced_horror-free</t>
   </si>
   <si>
-    <t>bgfade(sntzm_clark3F(1)_67,1)&amp;loadScript(sntzm_clark3F(2), 2)&amp;unlockmusic(Music14)</t>
+    <t>bgfade(sntzm_clark3F(2)_1,1)&amp;loadScript(sntzm_clark3F(2), 2)&amp;unlockmusic(Music14)</t>
   </si>
   <si>
     <r>
